--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_009.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_009.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="161">
   <si>
     <t>Sezione</t>
   </si>
@@ -300,6 +300,12 @@
   </si>
   <si>
     <t>Firmatario</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Atto nascita intestatario</t>
@@ -547,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.59765625" customWidth="true" bestFit="true"/>
@@ -2838,53 +2844,53 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="C100" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E101" s="2" t="s">
+      <c r="F101" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>103</v>
@@ -2893,7 +2899,7 @@
         <v>34</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>104</v>
@@ -2902,12 +2908,12 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>105</v>
@@ -2916,7 +2922,7 @@
         <v>34</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>106</v>
@@ -2925,12 +2931,12 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>107</v>
@@ -2939,7 +2945,7 @@
         <v>34</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>108</v>
@@ -2948,12 +2954,12 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>109</v>
@@ -2962,44 +2968,44 @@
         <v>34</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>112</v>
@@ -3008,44 +3014,44 @@
         <v>34</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>115</v>
@@ -3054,7 +3060,7 @@
         <v>34</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>116</v>
@@ -3063,12 +3069,12 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>117</v>
@@ -3077,7 +3083,7 @@
         <v>34</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>118</v>
@@ -3086,12 +3092,12 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>119</v>
@@ -3100,7 +3106,7 @@
         <v>34</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>120</v>
@@ -3109,44 +3115,44 @@
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="C112" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B113" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>126</v>
@@ -3160,7 +3166,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>127</v>
@@ -3169,7 +3175,7 @@
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>128</v>
@@ -3183,19 +3189,19 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
@@ -3206,16 +3212,16 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>131</v>
@@ -3229,16 +3235,16 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>133</v>
@@ -3252,7 +3258,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>134</v>
@@ -3261,7 +3267,7 @@
         <v>34</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>135</v>
@@ -3275,19 +3281,19 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="C119" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D119" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
@@ -3298,16 +3304,16 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>126</v>
@@ -3321,7 +3327,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>127</v>
@@ -3330,7 +3336,7 @@
         <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>128</v>
@@ -3344,19 +3350,19 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -3367,7 +3373,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>140</v>
@@ -3376,7 +3382,7 @@
         <v>34</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>141</v>
@@ -3390,7 +3396,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>142</v>
@@ -3399,7 +3405,7 @@
         <v>34</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>143</v>
@@ -3413,7 +3419,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>144</v>
@@ -3422,7 +3428,7 @@
         <v>34</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>145</v>
@@ -3436,7 +3442,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>146</v>
@@ -3445,7 +3451,7 @@
         <v>34</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>147</v>
@@ -3459,7 +3465,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>148</v>
@@ -3468,7 +3474,7 @@
         <v>34</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>149</v>
@@ -3482,19 +3488,19 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="C128" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
@@ -3505,16 +3511,16 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D129" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>155</v>
@@ -3528,24 +3534,47 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="C130" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E130" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E130" s="2" t="s">
+      <c r="F130" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F130" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G130" s="2" t="s">
+      <c r="B131" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G131" s="2" t="s">
         <v>19</v>
       </c>
     </row>
